--- a/output/pdf_financials_xlsx/REVX.xlsx
+++ b/output/pdf_financials_xlsx/REVX.xlsx
@@ -1665,10 +1665,10 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.02028</v>
+        <v>-1.248622</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0.002672</v>
+        <v>-2.404396</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-1.861868</v>
@@ -1938,19 +1938,19 @@
         <v>-0.597401</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.614171</v>
+        <v>-0.614171</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.200862</v>
+        <v>-1.200862</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.72616</v>
+        <v>-1.72616</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.583018</v>
+        <v>-0.583018</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.435946</v>
+        <v>-0.435946</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>-0.785924</v>
@@ -2175,19 +2175,19 @@
         <v>-0.597401</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.614171</v>
+        <v>-0.614171</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.200862</v>
+        <v>-1.200862</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.72616</v>
+        <v>-1.72616</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.583018</v>
+        <v>-0.583018</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.435946</v>
+        <v>-0.435946</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>-0.785924</v>
@@ -2416,13 +2416,13 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8.773871</v>
+        <v>-8.773871</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>17.155171</v>
+        <v>-17.155171</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>43.154</v>
+        <v>-43.154</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>6.2278</v>
+        <v>-6.2278</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>9.82405</v>
@@ -2831,10 +2831,10 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>3.196464344764213</v>
+        <v>196.8035356552358</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.2220128388562351</v>
+        <v>199.7779871611438</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>99.29337780342357</v>
@@ -46517,7 +46517,7 @@
         </is>
       </c>
       <c r="T346" s="5" t="n">
-        <v>0.435946</v>
+        <v>-0.435946</v>
       </c>
       <c r="U346" s="5" t="n">
         <v>-0.785924</v>
@@ -47897,10 +47897,10 @@
         </is>
       </c>
       <c r="T359" s="5" t="n">
-        <v>0.520946</v>
+        <v>-0.520946</v>
       </c>
       <c r="U359" s="5" t="n">
-        <v>0.702049</v>
+        <v>-0.702049</v>
       </c>
       <c r="V359" t="inlineStr">
         <is>
@@ -50477,13 +50477,13 @@
         </is>
       </c>
       <c r="R384" s="5" t="n">
-        <v>1.72616</v>
+        <v>-1.72616</v>
       </c>
       <c r="S384" s="5" t="n">
-        <v>0.583018</v>
+        <v>-0.583018</v>
       </c>
       <c r="T384" s="5" t="n">
-        <v>0.435946</v>
+        <v>-0.435946</v>
       </c>
       <c r="U384" t="inlineStr">
         <is>
@@ -50687,13 +50687,13 @@
         </is>
       </c>
       <c r="R386" s="5" t="n">
-        <v>1.72616</v>
+        <v>-1.72616</v>
       </c>
       <c r="S386" s="5" t="n">
-        <v>0.584268</v>
+        <v>-0.584268</v>
       </c>
       <c r="T386" s="5" t="n">
-        <v>0.520946</v>
+        <v>-0.520946</v>
       </c>
       <c r="U386" t="inlineStr">
         <is>
@@ -55836,10 +55836,10 @@
         </is>
       </c>
       <c r="Q435" s="5" t="n">
-        <v>1.200862</v>
+        <v>-1.200862</v>
       </c>
       <c r="R435" s="5" t="n">
-        <v>1.72616</v>
+        <v>-1.72616</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
@@ -57279,10 +57279,10 @@
         <v>-0.597401</v>
       </c>
       <c r="P449" s="5" t="n">
-        <v>0.614171</v>
+        <v>-0.614171</v>
       </c>
       <c r="Q449" s="5" t="n">
-        <v>1.200862</v>
+        <v>-1.200862</v>
       </c>
       <c r="R449" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/REVX.xlsx
+++ b/output/pdf_financials_xlsx/REVX.xlsx
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1273,13 +1273,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001561</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000546</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.109054</v>
+        <v>-1.129054</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.597401</v>
@@ -2500,13 +2500,13 @@
         <v>0.634451</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.203534</v>
+        <v>1.205095</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>1.875118</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.690316</v>
+        <v>0.690862</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>0.435946</v>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.108305</v>
+        <v>-1.128305</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.596427</v>
@@ -2658,13 +2658,13 @@
         <v>0.63523</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.204158</v>
+        <v>1.205719</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>1.875616</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.692311</v>
+        <v>0.6928569999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>0.435946</v>
@@ -2972,49 +2972,49 @@
         <v>0.278298</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.02713</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.146073</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.098922</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.183305</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.03531</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.07277500000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.403678</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.041126</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.003177</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.462861</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.659964</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.086436</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.09069099999999999</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.485986</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.753561</v>
       </c>
     </row>
     <row r="35">
@@ -3094,49 +3094,49 @@
         <v>0.285298</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0024</v>
+        <v>0.02953</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.0368</v>
+        <v>0.182873</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.00489</v>
+        <v>0.103812</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.01326</v>
+        <v>0.196565</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1e-05</v>
+        <v>0.03532</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1e-05</v>
+        <v>0.072785</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.403678</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.041126</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.003177</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.462861</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.659964</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.086436</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.12625</v>
+        <v>0.216941</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.210125</v>
+        <v>1.696111</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>3.667525</v>
+        <v>4.421086</v>
       </c>
     </row>
     <row r="37">
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.303617</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>0</v>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -49980,7 +49980,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -54826,7 +54826,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -57540,7 +57540,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
